--- a/output/pdf_financials_xlsx/STMN.xlsx
+++ b/output/pdf_financials_xlsx/STMN.xlsx
@@ -2213,16 +2213,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.591645</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.039189</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.039189</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.087453</v>
       </c>
     </row>
     <row r="93">
@@ -3520,7 +3520,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.591645</v>
       </c>

--- a/output/pdf_financials_xlsx/STMN.xlsx
+++ b/output/pdf_financials_xlsx/STMN.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002768</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009486</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002676</v>
       </c>
     </row>
     <row r="13">
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.046543</v>
+        <v>-0.049311</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.199473</v>
+        <v>-0.208959</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.112834</v>
+        <v>-0.118835</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.112834</v>
+        <v>-0.11551</v>
       </c>
     </row>
     <row r="28">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.046543</v>
+        <v>-0.049311</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.199473</v>
+        <v>-0.208959</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.112834</v>
+        <v>-0.118835</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.112834</v>
+        <v>-0.11551</v>
       </c>
     </row>
     <row r="30">
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.565758</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.237995</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.10018</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.061047</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.565758</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.237995</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.10018</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.061047</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.565758</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.237995</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.10018</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.06333900000000001</v>
+        <v>0.002292</v>
       </c>
     </row>
     <row r="49">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
